--- a/REPORTING MODULE/Chemist List -Alfez.xlsx
+++ b/REPORTING MODULE/Chemist List -Alfez.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY WORK FLOW\Emyris Onboard App\REPORTING MODULE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA02DE2-EC65-4020-A934-6689AF2418E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9618BE-996B-45CA-9EE3-BEF48DA5EED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="122">
-  <si>
-    <t>Sr</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="120">
   <si>
     <t>Name</t>
   </si>
@@ -55,9 +52,6 @@
   </si>
   <si>
     <t>Working Area</t>
-  </si>
-  <si>
-    <t>UID</t>
   </si>
   <si>
     <t>chirag bhai</t>
@@ -768,16 +762,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="112.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="112.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -805,1137 +800,1026 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>8866006878</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>8866006878</v>
-      </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>9016990052</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>9016990052</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>9510706706</v>
+      </c>
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>9510706706</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>8490881680</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>8490881680</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>9825234687</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>9825234687</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>9909960082</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>9909960082</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>7069071874</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>7069071874</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>8160557154</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>8160557154</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>7487026227</v>
+      </c>
+      <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>7487026227</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>6352694491</v>
+      </c>
+      <c r="G11" t="s">
         <v>40</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>6352694491</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>9624311480</v>
+      </c>
+      <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>9624311480</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>9974810911</v>
+      </c>
+      <c r="G13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>47</v>
       </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>9974810911</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14">
+        <v>9016825637</v>
+      </c>
+      <c r="G14" t="s">
         <v>50</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="G14">
-        <v>9016825637</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>9879853595</v>
+      </c>
+      <c r="G15" t="s">
         <v>53</v>
       </c>
-      <c r="C15" t="s">
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>54</v>
       </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>9879853595</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>9377049055</v>
+      </c>
+      <c r="G16" t="s">
         <v>56</v>
       </c>
-      <c r="C16" t="s">
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>57</v>
       </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>9377049055</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17">
+        <v>9638475003</v>
+      </c>
+      <c r="G17" t="s">
         <v>60</v>
       </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
-      <c r="G17">
-        <v>9638475003</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>9714589877</v>
+      </c>
+      <c r="G18" t="s">
         <v>63</v>
       </c>
-      <c r="C18" t="s">
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>64</v>
       </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>9714589877</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="B19" t="s">
         <v>65</v>
       </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
         <v>66</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19">
+        <v>9687615752</v>
+      </c>
+      <c r="G19" t="s">
         <v>67</v>
       </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>68</v>
       </c>
-      <c r="G19">
-        <v>9687615752</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="B20" t="s">
         <v>69</v>
       </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20">
+        <v>7972668693</v>
+      </c>
+      <c r="G20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>71</v>
       </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>7972668693</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21">
+        <v>7265019070</v>
+      </c>
+      <c r="G21" t="s">
         <v>73</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>74</v>
       </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>7265019070</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <v>9106657456</v>
+      </c>
+      <c r="G22" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>77</v>
       </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>9106657456</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="B23" t="s">
         <v>78</v>
       </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>9879538903</v>
+      </c>
+      <c r="G23" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>80</v>
       </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>9879538903</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="B24" t="s">
         <v>81</v>
       </c>
-      <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>6358838381</v>
+      </c>
+      <c r="G24" t="s">
         <v>82</v>
       </c>
-      <c r="C24" t="s">
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>83</v>
       </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>6358838381</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="B25" t="s">
         <v>84</v>
       </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25">
+        <v>9924097860</v>
+      </c>
+      <c r="G25" t="s">
         <v>85</v>
       </c>
-      <c r="C25" t="s">
+      <c r="H25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>86</v>
       </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>9924097860</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="B26" t="s">
         <v>87</v>
       </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>9904402122</v>
+      </c>
+      <c r="G26" t="s">
         <v>88</v>
       </c>
-      <c r="C26" t="s">
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>89</v>
       </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26">
-        <v>9904402122</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="B27" t="s">
         <v>90</v>
       </c>
-      <c r="I26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>8160996732</v>
+      </c>
+      <c r="G27" t="s">
         <v>91</v>
       </c>
-      <c r="C27" t="s">
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>92</v>
       </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27">
-        <v>8160996732</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="B28" t="s">
         <v>93</v>
       </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28">
+        <v>9316481528</v>
+      </c>
+      <c r="G28" t="s">
         <v>94</v>
       </c>
-      <c r="C28" t="s">
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>95</v>
       </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28">
-        <v>9316481528</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="B29" t="s">
         <v>96</v>
       </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
         <v>97</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29">
+        <v>7284975575</v>
+      </c>
+      <c r="G29" t="s">
         <v>98</v>
       </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>99</v>
       </c>
-      <c r="G29">
-        <v>7284975575</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="B30" t="s">
         <v>100</v>
       </c>
-      <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>7016124348</v>
+      </c>
+      <c r="G30" t="s">
         <v>101</v>
       </c>
-      <c r="C30" t="s">
+      <c r="H30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>102</v>
       </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30">
-        <v>7016124348</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="B31" t="s">
         <v>103</v>
       </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31">
+        <v>9725459727</v>
+      </c>
+      <c r="G31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
+      <c r="H31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>105</v>
       </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31">
-        <v>9725459727</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="B32" t="s">
         <v>106</v>
       </c>
-      <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32">
+        <v>9624788446</v>
+      </c>
+      <c r="G32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
+      <c r="H32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>108</v>
       </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32">
-        <v>9624788446</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33">
+        <v>9925653654</v>
+      </c>
+      <c r="G33" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="s">
+      <c r="H33" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>111</v>
       </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33">
-        <v>9925653654</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="B34" t="s">
         <v>112</v>
       </c>
-      <c r="I33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>7573050532</v>
+      </c>
+      <c r="G34" t="s">
         <v>113</v>
       </c>
-      <c r="C34" t="s">
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>114</v>
       </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34">
-        <v>7573050532</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="B35" t="s">
         <v>115</v>
       </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35">
+        <v>9974125531</v>
+      </c>
+      <c r="G35" t="s">
         <v>116</v>
       </c>
-      <c r="C35" t="s">
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>117</v>
       </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35">
-        <v>9974125531</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="B36" t="s">
         <v>118</v>
       </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36">
+        <v>9998992397</v>
+      </c>
+      <c r="G36" t="s">
         <v>119</v>
       </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36">
-        <v>9998992397</v>
-      </c>
       <c r="H36" t="s">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A37:K37 A18:J36 A2:J17 D38:K43" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A37:I37 A18:I36 A2:I17 C38:I43" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>